--- a/output/table_13_oecd_oda.xlsx
+++ b/output/table_13_oecd_oda.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -499,520 +499,920 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="C4">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D4">
-        <v>14.4</v>
+        <v>32.1</v>
       </c>
       <c r="E4">
-        <v>-16.6</v>
+        <v>-9.1</v>
       </c>
       <c r="F4">
-        <v>-7.4</v>
+        <v>-8</v>
       </c>
       <c r="G4">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="H4">
-        <v>15.073</v>
+        <v>1.728</v>
       </c>
       <c r="I4">
-        <v>55.6</v>
+        <v>48.1</v>
       </c>
       <c r="J4">
-        <v>44.4</v>
+        <v>51.9</v>
       </c>
       <c r="K4">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="L4">
-        <v>39.8</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B5">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="C5">
-        <v>9.300000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="E5">
-        <v>3.7</v>
+        <v>-0.8</v>
       </c>
       <c r="F5">
-        <v>-22</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>0.6899999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="H5">
-        <v>33.245</v>
+        <v>3.247</v>
       </c>
       <c r="I5">
-        <v>75.09999999999999</v>
+        <v>45.1</v>
       </c>
       <c r="J5">
-        <v>24.9</v>
+        <v>54.9</v>
       </c>
       <c r="K5">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
-        <v>22.4</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="B6">
-        <v>8.800000000000001</v>
+        <v>-0.6</v>
       </c>
       <c r="C6">
-        <v>6.5</v>
+        <v>0.3</v>
       </c>
       <c r="D6">
-        <v>16.1</v>
+        <v>-2.1</v>
       </c>
       <c r="E6">
-        <v>-17.5</v>
+        <v>9.4</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>-0.4</v>
       </c>
       <c r="G6">
-        <v>0.29</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H6">
-        <v>6.878</v>
+        <v>3.017</v>
       </c>
       <c r="I6">
-        <v>46.2</v>
+        <v>66.3</v>
       </c>
       <c r="J6">
-        <v>53.8</v>
+        <v>33.7</v>
       </c>
       <c r="K6">
-        <v>2.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L6">
-        <v>51.5</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B7">
-        <v>3.3</v>
+        <v>7.8</v>
       </c>
       <c r="C7">
-        <v>11.1</v>
+        <v>1.2</v>
       </c>
       <c r="D7">
-        <v>29.4</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>-17.4</v>
+        <v>-4.8</v>
       </c>
       <c r="F7">
-        <v>9.9</v>
+        <v>-18.5</v>
       </c>
       <c r="G7">
-        <v>0.24</v>
+        <v>0.46</v>
       </c>
       <c r="H7">
-        <v>4.124</v>
+        <v>1.367</v>
       </c>
       <c r="I7">
-        <v>36</v>
+        <v>54.3</v>
       </c>
       <c r="J7">
-        <v>64</v>
+        <v>45.7</v>
       </c>
       <c r="K7">
-        <v>4.1</v>
+        <v>8.9</v>
       </c>
       <c r="L7">
-        <v>59.9</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>-1.7</v>
+        <v>3.6</v>
       </c>
       <c r="D8">
-        <v>-13.1</v>
+        <v>14.4</v>
       </c>
       <c r="E8">
-        <v>6.4</v>
+        <v>-16.6</v>
       </c>
       <c r="F8">
-        <v>10.5</v>
+        <v>-7.4</v>
       </c>
       <c r="G8">
-        <v>0.21</v>
+        <v>0.47</v>
       </c>
       <c r="H8">
-        <v>3.655</v>
+        <v>15.073</v>
       </c>
       <c r="I8">
-        <v>81.40000000000001</v>
+        <v>55.6</v>
       </c>
       <c r="J8">
-        <v>18.6</v>
+        <v>44.4</v>
       </c>
       <c r="K8">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="L8">
-        <v>13</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="B9">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>2.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D9">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E9">
-        <v>-0.1</v>
+        <v>3.7</v>
       </c>
       <c r="F9">
-        <v>-8.4</v>
+        <v>-22</v>
       </c>
       <c r="G9">
-        <v>0.38</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H9">
-        <v>8.423</v>
+        <v>33.245</v>
       </c>
       <c r="I9">
-        <v>83.09999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="J9">
-        <v>16.9</v>
+        <v>24.9</v>
       </c>
       <c r="K9">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="L9">
-        <v>13.5</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>7.4</v>
+        <v>2.5</v>
       </c>
       <c r="D10">
-        <v>26.7</v>
+        <v>11.7</v>
       </c>
       <c r="E10">
-        <v>14.7</v>
+        <v>-14.8</v>
       </c>
       <c r="F10">
-        <v>-14.4</v>
+        <v>7.5</v>
       </c>
       <c r="G10">
-        <v>0.36</v>
+        <v>0.15</v>
       </c>
       <c r="H10">
-        <v>15.246</v>
+        <v>0.372</v>
       </c>
       <c r="I10">
-        <v>81.5</v>
+        <v>17.7</v>
       </c>
       <c r="J10">
-        <v>18.5</v>
+        <v>82.3</v>
       </c>
       <c r="K10">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="L10">
-        <v>15.5</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="B11">
-        <v>16.7</v>
+        <v>7.3</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>2.3</v>
       </c>
       <c r="D11">
-        <v>7.5</v>
+        <v>119.6</v>
       </c>
       <c r="E11">
-        <v>12.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F11">
-        <v>28.5</v>
+        <v>-11.5</v>
       </c>
       <c r="G11">
-        <v>0.22</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H11">
-        <v>4.234</v>
+        <v>2.542</v>
       </c>
       <c r="I11">
-        <v>80.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="J11">
-        <v>19.9</v>
+        <v>29.9</v>
       </c>
       <c r="K11">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="L11">
-        <v>13.4</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="B12">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C12">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="D12">
-        <v>-20.6</v>
+        <v>16.1</v>
       </c>
       <c r="E12">
-        <v>45.3</v>
+        <v>-17.5</v>
       </c>
       <c r="F12">
-        <v>0.8</v>
+        <v>12</v>
       </c>
       <c r="G12">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="H12">
-        <v>0.783</v>
+        <v>6.878</v>
       </c>
       <c r="I12">
-        <v>88</v>
+        <v>46.2</v>
       </c>
       <c r="J12">
-        <v>12</v>
+        <v>53.8</v>
       </c>
       <c r="K12">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="L12">
-        <v>5.9</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="B13">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="C13">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="D13">
-        <v>-3.8</v>
+        <v>4.1</v>
       </c>
       <c r="E13">
-        <v>26.7</v>
+        <v>2.8</v>
       </c>
       <c r="F13">
-        <v>-4.5</v>
+        <v>-0.3</v>
       </c>
       <c r="G13">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>4.905</v>
+        <v>0.596</v>
       </c>
       <c r="I13">
-        <v>78.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J13">
-        <v>21.1</v>
+        <v>29.6</v>
       </c>
       <c r="K13">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>12.3</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="B14">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>3.2</v>
+        <v>-1.5</v>
       </c>
       <c r="D14">
-        <v>16.5</v>
+        <v>29.7</v>
       </c>
       <c r="E14">
-        <v>7.7</v>
+        <v>2.1</v>
       </c>
       <c r="F14">
-        <v>-15.3</v>
+        <v>-2.5</v>
       </c>
       <c r="G14">
-        <v>0.48</v>
+        <v>0.61</v>
       </c>
       <c r="H14">
-        <v>4.557</v>
+        <v>7.444</v>
       </c>
       <c r="I14">
-        <v>78.7</v>
+        <v>69.2</v>
       </c>
       <c r="J14">
-        <v>21.3</v>
+        <v>30.8</v>
       </c>
       <c r="K14">
-        <v>5.6</v>
+        <v>7.9</v>
       </c>
       <c r="L14">
-        <v>15.6</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="B15">
-        <v>9.199999999999999</v>
+        <v>16.2</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>-3.9</v>
       </c>
       <c r="D15">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>9.199999999999999</v>
+        <v>-5.8</v>
       </c>
       <c r="F15">
-        <v>-17.3</v>
+        <v>20.5</v>
       </c>
       <c r="G15">
-        <v>0.45</v>
+        <v>0.19</v>
       </c>
       <c r="H15">
-        <v>16.27</v>
+        <v>0.572</v>
       </c>
       <c r="I15">
-        <v>78.3</v>
+        <v>17.7</v>
       </c>
       <c r="J15">
-        <v>21.7</v>
+        <v>82.3</v>
       </c>
       <c r="K15">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="L15">
-        <v>17.2</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>3.3</v>
+      </c>
+      <c r="C16">
+        <v>11.1</v>
+      </c>
+      <c r="D16">
+        <v>29.4</v>
+      </c>
+      <c r="E16">
+        <v>-17.4</v>
+      </c>
+      <c r="F16">
+        <v>9.9</v>
+      </c>
+      <c r="G16">
+        <v>0.24</v>
+      </c>
+      <c r="H16">
+        <v>4.124</v>
+      </c>
+      <c r="I16">
+        <v>36</v>
+      </c>
+      <c r="J16">
+        <v>64</v>
+      </c>
+      <c r="K16">
+        <v>4.1</v>
+      </c>
+      <c r="L16">
+        <v>59.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SWE</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>6.3</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17">
+        <v>2.6</v>
+      </c>
+      <c r="E17">
+        <v>-0.8</v>
+      </c>
+      <c r="F17">
+        <v>-14.4</v>
+      </c>
+      <c r="G17">
+        <v>0.76</v>
+      </c>
+      <c r="H17">
+        <v>4.829</v>
+      </c>
+      <c r="I17">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="J17">
+        <v>34.6</v>
+      </c>
+      <c r="K17">
+        <v>11.1</v>
+      </c>
+      <c r="L17">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <v>-1.7</v>
+      </c>
+      <c r="D18">
+        <v>-13.1</v>
+      </c>
+      <c r="E18">
+        <v>6.4</v>
+      </c>
+      <c r="F18">
+        <v>10.5</v>
+      </c>
+      <c r="G18">
+        <v>0.21</v>
+      </c>
+      <c r="H18">
+        <v>3.655</v>
+      </c>
+      <c r="I18">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="J18">
+        <v>18.6</v>
+      </c>
+      <c r="K18">
+        <v>5.6</v>
+      </c>
+      <c r="L18">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>7.1</v>
+      </c>
+      <c r="C19">
+        <v>2.2</v>
+      </c>
+      <c r="D19">
+        <v>43</v>
+      </c>
+      <c r="E19">
+        <v>-0.1</v>
+      </c>
+      <c r="F19">
+        <v>-8.4</v>
+      </c>
+      <c r="G19">
+        <v>0.38</v>
+      </c>
+      <c r="H19">
+        <v>8.423</v>
+      </c>
+      <c r="I19">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="J19">
+        <v>16.9</v>
+      </c>
+      <c r="K19">
+        <v>3.3</v>
+      </c>
+      <c r="L19">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>7.4</v>
+      </c>
+      <c r="D20">
+        <v>26.7</v>
+      </c>
+      <c r="E20">
+        <v>14.7</v>
+      </c>
+      <c r="F20">
+        <v>-14.4</v>
+      </c>
+      <c r="G20">
+        <v>0.36</v>
+      </c>
+      <c r="H20">
+        <v>15.246</v>
+      </c>
+      <c r="I20">
+        <v>81.5</v>
+      </c>
+      <c r="J20">
+        <v>18.5</v>
+      </c>
+      <c r="K20">
+        <v>3</v>
+      </c>
+      <c r="L20">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KOR</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>16.7</v>
+      </c>
+      <c r="C21">
+        <v>7.7</v>
+      </c>
+      <c r="D21">
+        <v>7.5</v>
+      </c>
+      <c r="E21">
+        <v>12.6</v>
+      </c>
+      <c r="F21">
+        <v>28.5</v>
+      </c>
+      <c r="G21">
+        <v>0.22</v>
+      </c>
+      <c r="H21">
+        <v>4.234</v>
+      </c>
+      <c r="I21">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="J21">
+        <v>19.9</v>
+      </c>
+      <c r="K21">
+        <v>6.5</v>
+      </c>
+      <c r="L21">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NZL</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>4.9</v>
+      </c>
+      <c r="C22">
+        <v>4.4</v>
+      </c>
+      <c r="D22">
+        <v>-20.6</v>
+      </c>
+      <c r="E22">
+        <v>45.3</v>
+      </c>
+      <c r="F22">
+        <v>0.8</v>
+      </c>
+      <c r="G22">
+        <v>0.32</v>
+      </c>
+      <c r="H22">
+        <v>0.783</v>
+      </c>
+      <c r="I22">
+        <v>88</v>
+      </c>
+      <c r="J22">
+        <v>12</v>
+      </c>
+      <c r="K22">
+        <v>6.1</v>
+      </c>
+      <c r="L22">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NOR</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>3.9</v>
+      </c>
+      <c r="C23">
+        <v>1.8</v>
+      </c>
+      <c r="D23">
+        <v>-3.8</v>
+      </c>
+      <c r="E23">
+        <v>26.7</v>
+      </c>
+      <c r="F23">
+        <v>-4.5</v>
+      </c>
+      <c r="G23">
+        <v>0.97</v>
+      </c>
+      <c r="H23">
+        <v>4.905</v>
+      </c>
+      <c r="I23">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="J23">
+        <v>21.1</v>
+      </c>
+      <c r="K23">
+        <v>8.9</v>
+      </c>
+      <c r="L23">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CHE</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>5.3</v>
+      </c>
+      <c r="C24">
+        <v>3.2</v>
+      </c>
+      <c r="D24">
+        <v>16.5</v>
+      </c>
+      <c r="E24">
+        <v>7.7</v>
+      </c>
+      <c r="F24">
+        <v>-15.3</v>
+      </c>
+      <c r="G24">
+        <v>0.48</v>
+      </c>
+      <c r="H24">
+        <v>4.557</v>
+      </c>
+      <c r="I24">
+        <v>78.7</v>
+      </c>
+      <c r="J24">
+        <v>21.3</v>
+      </c>
+      <c r="K24">
+        <v>5.6</v>
+      </c>
+      <c r="L24">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GBR</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>2.5</v>
+      </c>
+      <c r="E25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F25">
+        <v>-17.3</v>
+      </c>
+      <c r="G25">
+        <v>0.45</v>
+      </c>
+      <c r="H25">
+        <v>16.27</v>
+      </c>
+      <c r="I25">
+        <v>78.3</v>
+      </c>
+      <c r="J25">
+        <v>21.7</v>
+      </c>
+      <c r="K25">
+        <v>4.4</v>
+      </c>
+      <c r="L25">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B16">
+      <c r="B26">
         <v>9.300000000000001</v>
       </c>
-      <c r="C16">
+      <c r="C26">
         <v>2.9</v>
       </c>
-      <c r="D16">
+      <c r="D26">
         <v>18.5</v>
       </c>
-      <c r="E16">
+      <c r="E26">
         <v>3.1</v>
       </c>
-      <c r="F16">
+      <c r="F26">
         <v>-1</v>
       </c>
-      <c r="G16">
+      <c r="G26">
         <v>0.22</v>
       </c>
-      <c r="H16">
+      <c r="H26">
         <v>65.337</v>
       </c>
-      <c r="I16">
+      <c r="I26">
         <v>89.90000000000001</v>
       </c>
-      <c r="J16">
+      <c r="J26">
         <v>10.1</v>
       </c>
-      <c r="K16">
+      <c r="K26">
         <v>2.7</v>
       </c>
-      <c r="L16">
+      <c r="L26">
         <v>7.4</v>
       </c>
     </row>

--- a/output/table_13_oecd_oda.xlsx
+++ b/output/table_13_oecd_oda.xlsx
@@ -441,7 +441,7 @@
         <v>0.33</v>
       </c>
       <c r="H2">
-        <v>211.869</v>
+        <v>211.874</v>
       </c>
       <c r="I2">
         <v>75.8</v>
@@ -481,7 +481,7 @@
         <v>0.47</v>
       </c>
       <c r="H3">
-        <v>88.34999999999999</v>
+        <v>88.355</v>
       </c>
       <c r="I3">
         <v>62.3</v>
@@ -675,13 +675,13 @@
         <v>-16.6</v>
       </c>
       <c r="F8">
-        <v>-7.4</v>
+        <v>-7.3</v>
       </c>
       <c r="G8">
         <v>0.47</v>
       </c>
       <c r="H8">
-        <v>15.073</v>
+        <v>15.074</v>
       </c>
       <c r="I8">
         <v>55.6</v>
@@ -721,7 +721,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H9">
-        <v>33.245</v>
+        <v>33.249</v>
       </c>
       <c r="I9">
         <v>75.09999999999999</v>
@@ -829,10 +829,10 @@
         <v>6.5</v>
       </c>
       <c r="D12">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="E12">
-        <v>-17.5</v>
+        <v>-17.4</v>
       </c>
       <c r="F12">
         <v>12</v>
@@ -1112,10 +1112,10 @@
         <v>43</v>
       </c>
       <c r="E19">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="F19">
-        <v>-8.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G19">
         <v>0.38</v>
